--- a/PythonScripts/Energy4U_Kereskedelmi_és_Szolgáltató_Korlátolt_Felelősségű_Társaság_Beszamolo_Elemzes.xlsx
+++ b/PythonScripts/Energy4U_Kereskedelmi_és_Szolgáltató_Korlátolt_Felelősségű_Társaság_Beszamolo_Elemzes.xlsx
@@ -478,16 +478,16 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3063</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>18775</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>43386</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>36661</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -515,16 +515,16 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>36459</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>103731</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-42809</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-16102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -589,16 +589,16 @@
         <v>32983</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>24732</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="6">
@@ -626,16 +626,16 @@
         <v>1225</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>10441</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>15148</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>10221</v>
       </c>
     </row>
     <row r="7">
@@ -700,16 +700,16 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-50614</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-21438</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-30612</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-25930</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -737,16 +737,16 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3930</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>38660</v>
       </c>
       <c r="J9" t="n">
-        <v>15306</v>
+        <v>43386</v>
       </c>
       <c r="K9" t="n">
-        <v>12965</v>
+        <v>36661</v>
       </c>
     </row>
     <row r="10">
@@ -774,16 +774,16 @@
         <v>12983</v>
       </c>
       <c r="H10" t="n">
-        <v>25307</v>
+        <v>29917</v>
       </c>
       <c r="I10" t="n">
-        <v>10719</v>
+        <v>48266</v>
       </c>
       <c r="J10" t="n">
-        <v>158</v>
+        <v>31512</v>
       </c>
       <c r="K10" t="n">
-        <v>2744</v>
+        <v>14398</v>
       </c>
     </row>
     <row r="11">
@@ -811,16 +811,16 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>24732</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>15148</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>10221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -848,16 +848,16 @@
         <v>1913</v>
       </c>
       <c r="H12" t="n">
-        <v>575</v>
+        <v>2612</v>
       </c>
       <c r="I12" t="n">
-        <v>10441</v>
+        <v>16805</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>11297</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="13">
@@ -891,10 +891,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>86195</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>52763</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="14">
@@ -922,16 +922,16 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3479</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>36690</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-119709</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>-65474</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -959,16 +959,16 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-65831</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-115483</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-124084</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-90973</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1033,16 +1033,16 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-25370</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-26494</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>47702</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1070,10 +1070,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-5331</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-15834</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1107,16 +1107,16 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>41204</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>41204</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-21208</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1144,16 +1144,16 @@
         <v>10231</v>
       </c>
       <c r="H20" t="n">
-        <v>-10503</v>
+        <v>33396</v>
       </c>
       <c r="I20" t="n">
-        <v>1124</v>
+        <v>84956</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>93215</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>60187</v>
       </c>
     </row>
     <row r="21">
@@ -1187,10 +1187,10 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>93215</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>60187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1348,34 +1348,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="C26" t="n">
-        <v>73</v>
+        <v>193</v>
       </c>
       <c r="D26" t="n">
-        <v>74</v>
+        <v>194</v>
       </c>
       <c r="E26" t="n">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="F26" t="n">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="G26" t="n">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="H26" t="n">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="I26" t="n">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="J26" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="K26" t="n">
-        <v>81</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27">
@@ -1440,16 +1440,16 @@
         <v>49104</v>
       </c>
       <c r="H28" t="n">
-        <v>36459</v>
+        <v>61766</v>
       </c>
       <c r="I28" t="n">
-        <v>103731</v>
+        <v>114450</v>
       </c>
       <c r="J28" t="n">
-        <v>43386</v>
+        <v>101501</v>
       </c>
       <c r="K28" t="n">
-        <v>36661</v>
+        <v>70728</v>
       </c>
     </row>
     <row r="29">
@@ -1477,16 +1477,16 @@
         <v>34208</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>25307</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>10719</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>15306</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>12965</v>
       </c>
     </row>
     <row r="30">
@@ -1514,16 +1514,16 @@
         <v>32983</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>24732</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="31">
@@ -1810,16 +1810,16 @@
         <v>1225</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>10441</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>15148</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>10221</v>
       </c>
     </row>
     <row r="39">
@@ -2550,16 +2550,16 @@
         <v>14896</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>36459</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>103731</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>86195</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>52763</v>
       </c>
     </row>
     <row r="59">
@@ -2587,16 +2587,16 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>3930</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>38660</v>
       </c>
       <c r="J59" t="n">
-        <v>15306</v>
+        <v>43386</v>
       </c>
       <c r="K59" t="n">
-        <v>12965</v>
+        <v>36661</v>
       </c>
     </row>
     <row r="60">
@@ -2846,16 +2846,16 @@
         <v>12983</v>
       </c>
       <c r="H66" t="n">
-        <v>25307</v>
+        <v>29917</v>
       </c>
       <c r="I66" t="n">
-        <v>10719</v>
+        <v>48266</v>
       </c>
       <c r="J66" t="n">
-        <v>158</v>
+        <v>31512</v>
       </c>
       <c r="K66" t="n">
-        <v>2744</v>
+        <v>14398</v>
       </c>
     </row>
     <row r="67">
@@ -3179,16 +3179,16 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>24732</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>15148</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>10221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3438,16 +3438,16 @@
         <v>1913</v>
       </c>
       <c r="H82" t="n">
-        <v>575</v>
+        <v>2612</v>
       </c>
       <c r="I82" t="n">
-        <v>10441</v>
+        <v>16805</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>11297</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="83">
@@ -3555,10 +3555,10 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>86195</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>52763</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="86">
@@ -3697,16 +3697,16 @@
         <v>49104</v>
       </c>
       <c r="H89" t="n">
-        <v>33396</v>
+        <v>61766</v>
       </c>
       <c r="I89" t="n">
-        <v>84956</v>
+        <v>114450</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>101501</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>70728</v>
       </c>
     </row>
     <row r="90">
@@ -3734,16 +3734,16 @@
         <v>38873</v>
       </c>
       <c r="H90" t="n">
-        <v>29917</v>
+        <v>28370</v>
       </c>
       <c r="I90" t="n">
-        <v>48266</v>
+        <v>29494</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>8286</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>10541</v>
       </c>
     </row>
     <row r="91">
@@ -3771,16 +3771,16 @@
         <v>3000</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="J91" t="n">
-        <v>11297</v>
+        <v>3000</v>
       </c>
       <c r="K91" t="n">
-        <v>1704</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="92">
@@ -3845,16 +3845,16 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>2612</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>16805</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -3888,10 +3888,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>101501</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>70728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -3919,16 +3919,16 @@
         <v>-1054</v>
       </c>
       <c r="H95" t="n">
-        <v>61766</v>
+        <v>-5331</v>
       </c>
       <c r="I95" t="n">
-        <v>114450</v>
+        <v>-15834</v>
       </c>
       <c r="J95" t="n">
-        <v>8286</v>
+        <v>26494</v>
       </c>
       <c r="K95" t="n">
-        <v>10541</v>
+        <v>5287</v>
       </c>
     </row>
     <row r="96">
@@ -3956,16 +3956,16 @@
         <v>41204</v>
       </c>
       <c r="H96" t="n">
-        <v>28370</v>
+        <v>41204</v>
       </c>
       <c r="I96" t="n">
-        <v>29494</v>
+        <v>41204</v>
       </c>
       <c r="J96" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -3993,10 +3993,10 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -4104,16 +4104,16 @@
         <v>-4277</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>-10503</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1124</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>-21208</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="101">
@@ -4289,16 +4289,16 @@
         <v>10231</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>33396</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>84956</v>
       </c>
       <c r="J105" t="n">
-        <v>26494</v>
+        <v>93215</v>
       </c>
       <c r="K105" t="n">
-        <v>5287</v>
+        <v>60187</v>
       </c>
     </row>
     <row r="106">
@@ -4326,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>-5331</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>-15834</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -4511,16 +4511,16 @@
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>41204</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>41204</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>-21208</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>2254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -4918,16 +4918,16 @@
         <v>10231</v>
       </c>
       <c r="H122" t="n">
-        <v>-10503</v>
+        <v>33396</v>
       </c>
       <c r="I122" t="n">
-        <v>1124</v>
+        <v>84956</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>93215</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>60187</v>
       </c>
     </row>
     <row r="123">
@@ -5405,10 +5405,10 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>93215</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>60187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -7255,10 +7255,10 @@
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>-21208</v>
+        <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>2254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -7292,10 +7292,10 @@
         <v>1124</v>
       </c>
       <c r="J186" t="n">
-        <v>0</v>
+        <v>-21208</v>
       </c>
       <c r="K186" t="n">
-        <v>0</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="187">
@@ -7304,7 +7304,9 @@
           <t>MUTATO: Vagyon változása (%)</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr"/>
+      <c r="B187" t="n">
+        <v>0</v>
+      </c>
       <c r="C187" t="n">
         <v>-42.29421969789053</v>
       </c>
@@ -7321,16 +7323,16 @@
         <v>-32.52164353442353</v>
       </c>
       <c r="H187" t="n">
-        <v>-25.75146627565983</v>
+        <v>25.78608667318345</v>
       </c>
       <c r="I187" t="n">
-        <v>184.5141117419567</v>
+        <v>85.29611760515495</v>
       </c>
       <c r="J187" t="n">
-        <v>-58.17450906672066</v>
+        <v>-11.31411096548711</v>
       </c>
       <c r="K187" t="n">
-        <v>-15.50039183146638</v>
+        <v>-30.31792790218816</v>
       </c>
     </row>
     <row r="188">
@@ -7358,16 +7360,16 @@
         <v>-11.5095226759296</v>
       </c>
       <c r="H188" t="n">
-        <v>-14.06005032617622</v>
+        <v>-6.167659531769254</v>
       </c>
       <c r="I188" t="n">
-        <v>1.968908112665235</v>
+        <v>3.411491522020915</v>
       </c>
       <c r="J188" t="n">
-        <v>-8.780134263517692</v>
+        <v>1.444736243463618</v>
       </c>
       <c r="K188" t="n">
-        <v>-9.552476426172262</v>
+        <v>-2.701452956175221</v>
       </c>
     </row>
     <row r="189">
@@ -7395,13 +7397,17 @@
         <v>79.16463017269469</v>
       </c>
       <c r="H189" t="n">
-        <v>89.58258474068751</v>
+        <v>45.93141857980119</v>
       </c>
       <c r="I189" t="n">
-        <v>56.81293846226282</v>
-      </c>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
+        <v>25.77020532983836</v>
+      </c>
+      <c r="J189" t="n">
+        <v>8.163466369789459</v>
+      </c>
+      <c r="K189" t="n">
+        <v>14.90357425630585</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7428,20 +7434,16 @@
         <v>20.83536982730531</v>
       </c>
       <c r="H190" t="n">
-        <v>0</v>
+        <v>54.06858142019881</v>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>74.22979467016164</v>
+      </c>
+      <c r="J190" t="n">
+        <v>91.83653363021054</v>
+      </c>
+      <c r="K190" t="n">
+        <v>85.09642574369416</v>
       </c>
     </row>
     <row r="191">
@@ -7469,13 +7471,17 @@
         <v>100</v>
       </c>
       <c r="H191" t="n">
-        <v>89.58258474068751</v>
+        <v>100</v>
       </c>
       <c r="I191" t="n">
-        <v>56.81293846226282</v>
-      </c>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="J191" t="n">
+        <v>100</v>
+      </c>
+      <c r="K191" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7502,20 +7508,16 @@
         <v>26.31903892161655</v>
       </c>
       <c r="H192" t="n">
-        <v>0</v>
+        <v>117.7158970743743</v>
       </c>
       <c r="I192" t="n">
-        <v>0</v>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>288.0450261070048</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1124.969828626599</v>
+      </c>
+      <c r="K192" t="n">
+        <v>570.9799829238212</v>
       </c>
     </row>
     <row r="193">
@@ -7542,21 +7544,17 @@
       <c r="G193" t="n">
         <v>1295.766666666667</v>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="H193" t="n">
+        <v>945.6666666666667</v>
+      </c>
+      <c r="I193" t="n">
+        <v>983.1333333333333</v>
       </c>
       <c r="J193" t="n">
-        <v>0</v>
+        <v>276.2</v>
       </c>
       <c r="K193" t="n">
-        <v>0</v>
+        <v>351.3666666666667</v>
       </c>
     </row>
     <row r="194">
@@ -7581,19 +7579,17 @@
       <c r="G194" t="n">
         <v>-142.5333333333333</v>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>-inf</t>
-        </is>
+      <c r="H194" t="n">
+        <v>-350.0999999999999</v>
+      </c>
+      <c r="I194" t="n">
+        <v>37.46666666666658</v>
+      </c>
+      <c r="J194" t="n">
+        <v>-706.9333333333334</v>
       </c>
       <c r="K194" t="n">
-        <v>0</v>
+        <v>75.16666666666669</v>
       </c>
     </row>
     <row r="195">
@@ -7620,18 +7616,18 @@
       <c r="G195" t="n">
         <v>113.6371608980355</v>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
+      <c r="H195" t="n">
+        <v>112.1033706089224</v>
+      </c>
+      <c r="I195" t="n">
+        <v>275.1562645769195</v>
+      </c>
+      <c r="J195" t="n">
+        <v>54.13563308506468</v>
+      </c>
+      <c r="K195" t="n">
+        <v>81.30350944851523</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7657,25 +7653,17 @@
       <c r="G196" t="n">
         <v>113.6371608980355</v>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>-inf</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="H196" t="n">
+        <v>112.1033706089224</v>
+      </c>
+      <c r="I196" t="n">
+        <v>275.1562645769195</v>
+      </c>
+      <c r="J196" t="n">
+        <v>54.13563308506468</v>
+      </c>
+      <c r="K196" t="n">
+        <v>81.30350944851523</v>
       </c>
     </row>
   </sheetData>
